--- a/config/除湿机.xlsx
+++ b/config/除湿机.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18569" windowHeight="11268"/>
+    <workbookView windowWidth="22010" windowHeight="12332" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="遥测" sheetId="1" r:id="rId1"/>
+    <sheet name="遥调" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="49">
   <si>
     <t>序号</t>
   </si>
@@ -75,6 +76,105 @@
   </si>
   <si>
     <t>告警位</t>
+  </si>
+  <si>
+    <t>状态</t>
+  </si>
+  <si>
+    <t>U32</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>HoldingRegisters</t>
+  </si>
+  <si>
+    <t>ABCD</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>{"en":"state"}</t>
+  </si>
+  <si>
+    <t>故障</t>
+  </si>
+  <si>
+    <t>fault</t>
+  </si>
+  <si>
+    <t>{"en":"Fault"}</t>
+  </si>
+  <si>
+    <t>温度</t>
+  </si>
+  <si>
+    <t>I16</t>
+  </si>
+  <si>
+    <t>°C</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>temperature</t>
+  </si>
+  <si>
+    <t>{"en":"temperature"}</t>
+  </si>
+  <si>
+    <t>湿度</t>
+  </si>
+  <si>
+    <t>U16</t>
+  </si>
+  <si>
+    <t>%RH</t>
+  </si>
+  <si>
+    <t>humidity</t>
+  </si>
+  <si>
+    <t>{"en":"humidity"}</t>
+  </si>
+  <si>
+    <t>NTC1 温度</t>
+  </si>
+  <si>
+    <t>ntc1Temperature</t>
+  </si>
+  <si>
+    <t>{"en":"NTC1 temperature"}</t>
+  </si>
+  <si>
+    <t>NTC2 温度</t>
+  </si>
+  <si>
+    <t>ntc2Temperature</t>
+  </si>
+  <si>
+    <t>{"en":"NTC2 temperature"}</t>
+  </si>
+  <si>
+    <t>除湿设定点</t>
+  </si>
+  <si>
+    <t>dehumidificationSetPoint</t>
+  </si>
+  <si>
+    <t>{"en":"Dehumidification set point"}</t>
+  </si>
+  <si>
+    <t>除湿回差</t>
+  </si>
+  <si>
+    <t>dehumidificationHysteresis</t>
+  </si>
+  <si>
+    <t>{"en":"Dehumidification hysteresis"}</t>
   </si>
 </sst>
 </file>
@@ -550,9 +650,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -698,12 +796,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -757,221 +856,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </tableStyle>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -981,9 +866,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="WPS">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -991,42 +876,42 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4874CB"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EE822F"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="F2BA02"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="75BD42"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="30C0B4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="E54C5E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0026E5"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="7E1FAD"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="WPS">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -1055,13 +940,12 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -1090,135 +974,171 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="WPS">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumOff val="17500"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:hueOff val="-2520000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:gradFill>
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="phClr">
-                  <a:hueOff val="-4200000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="phClr"/>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="2700000" scaled="1"/>
-          </a:gradFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:schemeClr val="phClr">
-                <a:alpha val="60000"/>
-              </a:schemeClr>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1230,8 +1150,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P1"/>
-  <sheetFormatPr defaultColWidth="9.03174603174603" defaultRowHeight="18"/>
+  <dimension ref="A1:P7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="6"/>
+  <cols>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="10.1031746031746" style="2" customWidth="1"/>
+    <col min="3" max="6" width="9" style="2"/>
+    <col min="7" max="7" width="16.7222222222222" style="2" customWidth="1"/>
+    <col min="8" max="12" width="9" style="2"/>
+    <col min="13" max="13" width="16.7857142857143" style="2" customWidth="1"/>
+    <col min="14" max="14" width="25.2380952380952" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
+  </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:16">
       <c r="A1" s="1" t="s">
@@ -1281,6 +1211,478 @@
       </c>
       <c r="P1" s="1" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="2">
+        <v>4105</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="2">
+        <v>2</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="2">
+        <v>4107</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="2">
+        <v>4109</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="2">
+        <v>4110</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="2">
+        <v>4111</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="2">
+        <v>4112</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:P3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="2"/>
+  <cols>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="10.1031746031746" style="2" customWidth="1"/>
+    <col min="3" max="6" width="9" style="2"/>
+    <col min="7" max="7" width="16.7222222222222" style="2" customWidth="1"/>
+    <col min="8" max="12" width="9" style="2"/>
+    <col min="13" max="13" width="26.3968253968254" style="2" customWidth="1"/>
+    <col min="14" max="14" width="34.1746031746032" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:16">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="2">
+        <v>2000</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="2">
+        <v>28721</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="2">
+        <v>2001</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="2">
+        <v>28722</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
